--- a/math/05二次根式.xlsx
+++ b/math/05二次根式.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10914"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zimu/Documents/data-analytics/math/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C255CF3-9A43-FD42-95AE-5BAFEE07EB8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72622C5E-D2EE-D645-BC02-4B1AEA342521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{6D826E80-E51A-2441-9C97-4DF77565BC60}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="62">
   <si>
     <t>1、</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -222,6 +222,82 @@
   </si>
   <si>
     <t>消元：2x+x+y-y=9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3、</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一元二次方程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>“一元”只含有1个未知数（通常是x）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>“二次”未知数最高次数是2（即x2项存在，且a&lt;&gt;0，否则退化为一次方程）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>“等式”用等号连接，是整式方程（分母不含未知数）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ax2+bx+c=0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判别式 Δ=b2-4ac 作用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Δ&gt;0 方程有两个不相等的实数根</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Δ=0 方程有两个相等的实数根（即一个实根）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Δ&lt;0 方程无实数根（但在复数范围内有两个虚根）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>求根公式 x=-b+-√b2-4ac/2a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>首先要判断方程是否有解</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3x2+4x+1=0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>a=3 b=4 c=1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>代入判别式 Δ=16-4*3*1=4&gt;0 说明有两个实数根</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x=-4+-√4/2*3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x=-4+-2/6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x2=-4-2/6=-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x1=-4+2/6=-1/3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -641,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97BD63F6-1F0D-6D42-AA3C-48FA974F81A5}">
-  <dimension ref="B3:J58"/>
+  <dimension ref="B3:J85"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="16384" width="10.83203125" style="1"/>
@@ -796,7 +872,7 @@
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B45" s="1" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>31</v>
@@ -807,22 +883,22 @@
         <v>32</v>
       </c>
     </row>
-    <row r="49" spans="3:6" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.15">
       <c r="C49" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="50" spans="3:6" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
       <c r="C50" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="51" spans="3:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="C51" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="53" spans="3:6" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
       <c r="C53" s="1" t="s">
         <v>36</v>
       </c>
@@ -830,7 +906,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="54" spans="3:6" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D54" s="1" t="s">
         <v>37</v>
       </c>
@@ -838,7 +914,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="55" spans="3:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D55" s="1" t="s">
         <v>38</v>
       </c>
@@ -846,19 +922,112 @@
         <v>41</v>
       </c>
     </row>
-    <row r="56" spans="3:6" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D56" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="57" spans="3:6" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D57" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="58" spans="3:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D58" s="1" t="s">
         <v>41</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B61" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C63" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C64" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="65" spans="3:3" x14ac:dyDescent="0.15">
+      <c r="C65" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="67" spans="3:3" x14ac:dyDescent="0.15">
+      <c r="C67" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="69" spans="3:3" x14ac:dyDescent="0.15">
+      <c r="C69" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="70" spans="3:3" x14ac:dyDescent="0.15">
+      <c r="C70" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="71" spans="3:3" x14ac:dyDescent="0.15">
+      <c r="C71" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="72" spans="3:3" x14ac:dyDescent="0.15">
+      <c r="C72" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="74" spans="3:3" x14ac:dyDescent="0.15">
+      <c r="C74" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="76" spans="3:3" x14ac:dyDescent="0.15">
+      <c r="C76" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="77" spans="3:3" x14ac:dyDescent="0.15">
+      <c r="C77" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="78" spans="3:3" x14ac:dyDescent="0.15">
+      <c r="C78" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="80" spans="3:3" x14ac:dyDescent="0.15">
+      <c r="C80" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
+      <c r="C82" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="83" spans="3:3" x14ac:dyDescent="0.15">
+      <c r="C83" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="84" spans="3:3" x14ac:dyDescent="0.15">
+      <c r="C84" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="85" spans="3:3" x14ac:dyDescent="0.15">
+      <c r="C85" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/math/05二次根式.xlsx
+++ b/math/05二次根式.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zimu/Documents/data-analytics/math/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72622C5E-D2EE-D645-BC02-4B1AEA342521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{304D8C60-2B3C-D942-87D4-24CB9736DD99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{6D826E80-E51A-2441-9C97-4DF77565BC60}"/>
   </bookViews>
